--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DDV_HRM-2031-0100/Panel 7/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DDV_HRM-2031-0100/Panel 7/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
@@ -460,13 +460,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.66615</v>
+        <v>16.7257</v>
       </c>
       <c r="D2" t="n">
         <v>16.30937</v>
       </c>
       <c r="E2" t="n">
-        <v>16.7257</v>
+        <v>16.66615</v>
       </c>
       <c r="F2" t="n">
         <v>42.75199</v>
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>16.81762</v>
+      </c>
+      <c r="D3" t="n">
+        <v>16.32506</v>
+      </c>
+      <c r="E3" t="n">
         <v>16.77197</v>
-      </c>
-      <c r="D3" t="n">
-        <v>16.81762</v>
-      </c>
-      <c r="E3" t="n">
-        <v>16.32506</v>
       </c>
       <c r="F3" t="n">
         <v>42.36636</v>
@@ -589,13 +589,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.43233</v>
+        <v>16.4689</v>
       </c>
       <c r="D7" t="n">
         <v>16.0675</v>
       </c>
       <c r="E7" t="n">
-        <v>16.4689</v>
+        <v>16.43233</v>
       </c>
       <c r="F7" t="n">
         <v>21.87662</v>
@@ -614,10 +614,10 @@
         <v>16.41796</v>
       </c>
       <c r="D8" t="n">
+        <v>16.37816</v>
+      </c>
+      <c r="E8" t="n">
         <v>16.3848</v>
-      </c>
-      <c r="E8" t="n">
-        <v>16.37816</v>
       </c>
       <c r="F8" t="n">
         <v>21.40401</v>
